--- a/common/store/excel/Members Draw list 09.01.2026.xlsx
+++ b/common/store/excel/Members Draw list 09.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nigelpage/repos/GitHub/hbc/common/store/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1E52F4-095A-A244-8C7E-DF6F199BAE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B84D08-1F3D-B14B-9174-5E1263DA37E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="6100" windowWidth="29040" windowHeight="15720" xr2:uid="{F6BF9B91-7150-4350-8DCF-41A4FE9B5CF8}"/>
+    <workbookView xWindow="1980" yWindow="6100" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F6BF9B91-7150-4350-8DCF-41A4FE9B5CF8}"/>
   </bookViews>
   <sheets>
     <sheet name="BOWLING" sheetId="1" r:id="rId1"/>
@@ -2758,11 +2758,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6958,7 +6957,7 @@
         <v>13</v>
       </c>
       <c r="H162" t="str">
-        <f t="shared" ref="H162:H171" si="5">_xlfn.CONCAT(A162, " ",C162, " ",D162)</f>
+        <f>_xlfn.CONCAT(A162, " ",C162, " ",D162)</f>
         <v>302 Bradley Smith</v>
       </c>
     </row>
@@ -6982,7 +6981,7 @@
         <v>13</v>
       </c>
       <c r="H163" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.CONCAT(A163, " ",C163, " ",D163)</f>
         <v>303 Scott Rees</v>
       </c>
     </row>
@@ -7006,7 +7005,7 @@
         <v>13</v>
       </c>
       <c r="H164" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.CONCAT(A164, " ",C164, " ",D164)</f>
         <v>306 Rick Sherwen</v>
       </c>
     </row>
@@ -7030,7 +7029,7 @@
         <v>13</v>
       </c>
       <c r="H165" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.CONCAT(A165, " ",C165, " ",D165)</f>
         <v>307 Henryk Grossek</v>
       </c>
     </row>
@@ -7054,7 +7053,7 @@
         <v>13</v>
       </c>
       <c r="H166" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.CONCAT(A166, " ",C166, " ",D166)</f>
         <v>308 Deborah Grossek</v>
       </c>
     </row>
@@ -7078,7 +7077,7 @@
         <v>13</v>
       </c>
       <c r="H167" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.CONCAT(A167, " ",C167, " ",D167)</f>
         <v>313 Gordon Thomson</v>
       </c>
     </row>
@@ -7102,7 +7101,7 @@
         <v>13</v>
       </c>
       <c r="H168" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.CONCAT(A168, " ",C168, " ",D168)</f>
         <v>316 Rick Bennett</v>
       </c>
     </row>
@@ -7126,7 +7125,7 @@
         <v>13</v>
       </c>
       <c r="H169" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.CONCAT(A169, " ",C169, " ",D169)</f>
         <v>318 Adam Sledge</v>
       </c>
     </row>
@@ -7150,3697 +7149,3673 @@
         <v>13</v>
       </c>
       <c r="H170" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.CONCAT(A170, " ",C170, " ",D170)</f>
         <v>300 Danny Simmons</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A171">
-        <v>321</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="C171" t="s">
-        <v>888</v>
-      </c>
-      <c r="D171" t="s">
-        <v>430</v>
-      </c>
-      <c r="E171" t="s">
-        <v>889</v>
-      </c>
-      <c r="F171" t="s">
-        <v>13</v>
-      </c>
-      <c r="H171" t="str">
-        <f t="shared" si="5"/>
-        <v>321 Richard Dixon</v>
       </c>
     </row>
     <row r="306" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H306" t="str">
-        <f t="shared" ref="H306:H369" si="6">_xlfn.CONCAT(A306, " ",C306, " ",D306)</f>
+        <f t="shared" ref="H306:H369" si="5">_xlfn.CONCAT(A306, " ",C306, " ",D306)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="307" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H307" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="308" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H308" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="309" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H309" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="310" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H310" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="311" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H311" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="312" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H312" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="313" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H313" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="314" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H314" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="315" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H315" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="316" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H316" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="317" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H317" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="318" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H318" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="319" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H319" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="320" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H320" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="321" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H321" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="322" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H322" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="323" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H323" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="324" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H324" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="325" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H325" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="326" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H326" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="327" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H327" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="328" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H328" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="329" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H329" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="330" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H330" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="331" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H331" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="332" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H332" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="333" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H333" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="334" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H334" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="335" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H335" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="336" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H336" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="337" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H337" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="338" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H338" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="339" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H339" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="340" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H340" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="341" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H341" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="342" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H342" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="343" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H343" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="344" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H344" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="345" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H345" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="346" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H346" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="347" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H347" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="348" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H348" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="349" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H349" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="350" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H350" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="351" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H351" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="352" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H352" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="353" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H353" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="354" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H354" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="355" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H355" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="356" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H356" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="357" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H357" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="358" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H358" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="359" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H359" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="360" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H360" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="361" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H361" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="362" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H362" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="363" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H363" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="364" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H364" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="365" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H365" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="366" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H366" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="367" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H367" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="368" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H368" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="369" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H369" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="370" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H370" t="str">
-        <f t="shared" ref="H370:H433" si="7">_xlfn.CONCAT(A370, " ",C370, " ",D370)</f>
+        <f t="shared" ref="H370:H433" si="6">_xlfn.CONCAT(A370, " ",C370, " ",D370)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="371" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H371" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="372" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H372" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="373" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H373" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="374" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H374" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="375" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H375" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="376" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H376" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="377" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H377" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="378" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H378" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="379" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H379" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="380" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H380" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="381" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H381" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="382" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H382" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="383" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H383" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="384" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H384" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="385" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H385" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="386" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H386" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="387" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H387" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="388" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H388" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="389" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H389" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="390" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H390" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="391" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H391" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="392" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H392" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="393" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H393" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="394" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H394" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="395" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H395" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="396" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H396" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="397" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H397" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="398" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H398" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="399" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H399" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="400" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H400" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="401" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H401" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="402" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H402" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="403" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H403" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="404" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H404" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="405" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H405" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="406" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H406" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="407" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H407" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="408" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H408" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="409" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H409" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="410" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H410" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="411" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H411" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="412" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H412" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="413" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H413" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="414" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H414" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="415" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H415" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="416" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H416" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="417" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H417" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="418" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H418" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="419" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H419" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="420" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H420" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="421" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H421" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="422" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H422" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="423" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H423" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="424" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H424" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="425" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H425" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="426" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H426" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="427" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H427" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="428" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H428" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="429" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H429" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="430" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H430" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="431" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H431" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="432" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H432" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="433" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H433" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="434" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H434" t="str">
-        <f t="shared" ref="H434:H497" si="8">_xlfn.CONCAT(A434, " ",C434, " ",D434)</f>
+        <f t="shared" ref="H434:H497" si="7">_xlfn.CONCAT(A434, " ",C434, " ",D434)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="435" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H435" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="436" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H436" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="437" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H437" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="438" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H438" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="439" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H439" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="440" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H440" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="441" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H441" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="442" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H442" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="443" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H443" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="444" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H444" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="445" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H445" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="446" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H446" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="447" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H447" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="448" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H448" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="449" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H449" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="450" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H450" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="451" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H451" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="452" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H452" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="453" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H453" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="454" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H454" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="455" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H455" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="456" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H456" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="457" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H457" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="458" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H458" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="459" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H459" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="460" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H460" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="461" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H461" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="462" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H462" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="463" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H463" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="464" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H464" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="465" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H465" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="466" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H466" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="467" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H467" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="468" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H468" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="469" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H469" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="470" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H470" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="471" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H471" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="472" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H472" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="473" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H473" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="474" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H474" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="475" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H475" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="476" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H476" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="477" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H477" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="478" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H478" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="479" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H479" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="480" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H480" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="481" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H481" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="482" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H482" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="483" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H483" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="484" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H484" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="485" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H485" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="486" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H486" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="487" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H487" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="488" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H488" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="489" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H489" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="490" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H490" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="491" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H491" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="492" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H492" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="493" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H493" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="494" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H494" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="495" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H495" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="496" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H496" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="497" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H497" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="498" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H498" t="str">
-        <f t="shared" ref="H498:H561" si="9">_xlfn.CONCAT(A498, " ",C498, " ",D498)</f>
+        <f t="shared" ref="H498:H561" si="8">_xlfn.CONCAT(A498, " ",C498, " ",D498)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="499" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H499" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="500" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H500" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="501" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H501" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="502" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H502" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="503" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H503" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="504" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H504" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="505" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H505" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="506" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H506" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="507" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H507" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="508" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H508" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="509" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H509" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="510" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H510" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="511" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H511" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="512" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H512" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="513" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H513" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="514" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H514" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="515" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H515" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="516" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H516" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="517" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H517" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="518" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H518" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="519" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H519" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="520" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H520" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="521" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H521" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="522" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H522" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="523" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H523" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="524" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H524" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="525" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H525" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="526" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H526" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="527" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H527" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="528" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H528" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="529" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H529" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="530" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H530" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="531" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H531" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="532" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H532" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="533" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H533" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="534" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H534" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="535" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H535" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="536" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H536" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="537" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H537" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="538" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H538" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="539" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H539" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="540" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H540" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="541" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H541" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="542" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H542" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="543" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H543" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="544" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H544" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="545" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H545" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="546" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H546" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="547" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H547" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="548" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H548" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="549" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H549" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="550" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H550" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="551" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H551" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="552" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H552" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="553" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H553" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="554" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H554" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="555" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H555" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="556" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H556" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="557" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H557" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="558" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H558" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="559" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H559" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="560" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H560" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="561" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H561" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="562" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H562" t="str">
-        <f t="shared" ref="H562:H625" si="10">_xlfn.CONCAT(A562, " ",C562, " ",D562)</f>
+        <f t="shared" ref="H562:H625" si="9">_xlfn.CONCAT(A562, " ",C562, " ",D562)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="563" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H563" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="564" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H564" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="565" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H565" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="566" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H566" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="567" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H567" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="568" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H568" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="569" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H569" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="570" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H570" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="571" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H571" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="572" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H572" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="573" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H573" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="574" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H574" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="575" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H575" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="576" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H576" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="577" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H577" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="578" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H578" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="579" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H579" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="580" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H580" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="581" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H581" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="582" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H582" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="583" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H583" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="584" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H584" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="585" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H585" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="586" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H586" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="587" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H587" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="588" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H588" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="589" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H589" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="590" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H590" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="591" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H591" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="592" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H592" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="593" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H593" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="594" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H594" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="595" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H595" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="596" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H596" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="597" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H597" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="598" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H598" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="599" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H599" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="600" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H600" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="601" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H601" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="602" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H602" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="603" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H603" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="604" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H604" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="605" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H605" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="606" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H606" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="607" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H607" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="608" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H608" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="609" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H609" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="610" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H610" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="611" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H611" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="612" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H612" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="613" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H613" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="614" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H614" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="615" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H615" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="616" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H616" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="617" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H617" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="618" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H618" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="619" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H619" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="620" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H620" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="621" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H621" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="622" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H622" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="623" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H623" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="624" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H624" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="625" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H625" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="626" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H626" t="str">
-        <f t="shared" ref="H626:H689" si="11">_xlfn.CONCAT(A626, " ",C626, " ",D626)</f>
+        <f t="shared" ref="H626:H689" si="10">_xlfn.CONCAT(A626, " ",C626, " ",D626)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="627" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H627" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="628" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H628" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="629" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H629" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="630" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H630" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="631" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H631" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="632" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H632" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="633" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H633" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="634" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H634" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="635" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H635" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="636" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H636" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="637" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H637" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="638" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H638" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="639" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H639" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="640" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H640" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="641" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H641" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="642" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H642" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="643" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H643" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="644" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H644" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="645" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H645" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="646" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H646" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="647" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H647" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="648" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H648" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="649" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H649" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="650" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H650" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="651" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H651" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="652" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H652" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="653" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H653" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="654" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H654" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="655" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H655" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="656" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H656" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="657" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H657" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="658" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H658" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="659" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H659" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="660" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H660" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="661" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H661" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="662" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H662" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="663" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H663" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="664" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H664" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="665" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H665" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="666" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H666" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="667" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H667" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="668" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H668" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="669" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H669" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="670" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H670" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="671" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H671" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="672" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H672" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="673" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H673" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="674" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H674" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="675" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H675" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="676" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H676" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="677" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H677" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="678" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H678" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="679" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H679" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="680" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H680" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="681" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H681" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="682" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H682" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="683" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H683" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="684" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H684" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="685" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H685" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="686" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H686" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="687" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H687" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="688" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H688" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="689" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H689" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="690" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H690" t="str">
-        <f t="shared" ref="H690:H753" si="12">_xlfn.CONCAT(A690, " ",C690, " ",D690)</f>
+        <f t="shared" ref="H690:H753" si="11">_xlfn.CONCAT(A690, " ",C690, " ",D690)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="691" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H691" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="692" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H692" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="693" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H693" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="694" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H694" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="695" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H695" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="696" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H696" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="697" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H697" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="698" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H698" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="699" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H699" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="700" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H700" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="701" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H701" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="702" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H702" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="703" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H703" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="704" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H704" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="705" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H705" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="706" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H706" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="707" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H707" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="708" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H708" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="709" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H709" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="710" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H710" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="711" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H711" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="712" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H712" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="713" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H713" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="714" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H714" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="715" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H715" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="716" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H716" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="717" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H717" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="718" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H718" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="719" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H719" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="720" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H720" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="721" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H721" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="722" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H722" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="723" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H723" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="724" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H724" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="725" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H725" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="726" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H726" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="727" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H727" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="728" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H728" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="729" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H729" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="730" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H730" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="731" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H731" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="732" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H732" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="733" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H733" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="734" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H734" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="735" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H735" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="736" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H736" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="737" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H737" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="738" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H738" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="739" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H739" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="740" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H740" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="741" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H741" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="742" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H742" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="743" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H743" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="744" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H744" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="745" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H745" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="746" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H746" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="747" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H747" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="748" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H748" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="749" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H749" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="750" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H750" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="751" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H751" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="752" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H752" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="753" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H753" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="754" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H754" t="str">
-        <f t="shared" ref="H754:H817" si="13">_xlfn.CONCAT(A754, " ",C754, " ",D754)</f>
+        <f t="shared" ref="H754:H817" si="12">_xlfn.CONCAT(A754, " ",C754, " ",D754)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="755" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H755" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="756" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H756" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="757" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H757" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="758" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H758" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="759" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H759" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="760" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H760" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="761" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H761" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="762" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H762" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="763" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H763" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="764" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H764" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="765" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H765" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="766" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H766" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="767" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H767" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="768" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H768" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="769" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H769" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="770" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H770" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="771" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H771" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="772" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H772" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="773" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H773" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="774" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H774" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="775" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H775" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="776" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H776" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="777" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H777" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="778" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H778" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="779" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H779" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="780" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H780" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="781" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H781" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="782" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H782" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="783" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H783" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="784" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H784" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="785" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H785" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="786" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H786" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="787" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H787" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="788" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H788" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="789" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H789" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="790" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H790" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="791" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H791" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="792" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H792" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="793" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H793" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="794" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H794" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="795" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H795" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="796" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H796" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="797" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H797" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="798" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H798" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="799" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H799" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="800" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H800" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="801" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H801" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="802" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H802" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="803" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H803" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="804" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H804" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="805" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H805" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="806" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H806" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="807" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H807" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="808" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H808" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="809" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H809" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="810" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H810" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="811" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H811" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="812" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H812" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="813" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H813" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="814" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H814" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="815" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H815" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="816" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H816" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="817" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H817" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="818" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H818" t="str">
-        <f t="shared" ref="H818:H881" si="14">_xlfn.CONCAT(A818, " ",C818, " ",D818)</f>
+        <f t="shared" ref="H818:H881" si="13">_xlfn.CONCAT(A818, " ",C818, " ",D818)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="819" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H819" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="820" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H820" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="821" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H821" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="822" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H822" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="823" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H823" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="824" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H824" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="825" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H825" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="826" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H826" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="827" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H827" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="828" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H828" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="829" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H829" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="830" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H830" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="831" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H831" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="832" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H832" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="833" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H833" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="834" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H834" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="835" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H835" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="836" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H836" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="837" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H837" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="838" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H838" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="839" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H839" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="840" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H840" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="841" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H841" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="842" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H842" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="843" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H843" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="844" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H844" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="845" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H845" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="846" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H846" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="847" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H847" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="848" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H848" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="849" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H849" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="850" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H850" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="851" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H851" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="852" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H852" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="853" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H853" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="854" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H854" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="855" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H855" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="856" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H856" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="857" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H857" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="858" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H858" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="859" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H859" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="860" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H860" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="861" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H861" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="862" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H862" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="863" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H863" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="864" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H864" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="865" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H865" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="866" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H866" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="867" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H867" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="868" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H868" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="869" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H869" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="870" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H870" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="871" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H871" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="872" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H872" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="873" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H873" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="874" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H874" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="875" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H875" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="876" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H876" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="877" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H877" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="878" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H878" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="879" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H879" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="880" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H880" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="881" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H881" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="882" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H882" t="str">
-        <f t="shared" ref="H882:H916" si="15">_xlfn.CONCAT(A882, " ",C882, " ",D882)</f>
+        <f t="shared" ref="H882:H916" si="14">_xlfn.CONCAT(A882, " ",C882, " ",D882)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="883" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H883" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="884" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H884" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="885" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H885" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="886" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H886" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="887" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H887" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="888" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H888" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="889" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H889" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="890" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H890" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="891" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H891" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="892" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H892" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="893" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H893" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="894" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H894" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="895" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H895" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="896" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H896" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="897" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H897" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="898" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H898" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="899" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H899" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="900" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H900" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="901" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H901" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="902" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H902" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="903" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H903" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="904" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H904" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="905" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H905" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="906" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H906" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="907" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H907" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="908" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H908" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="909" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H909" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="910" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H910" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="911" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H911" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="912" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H912" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="913" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H913" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="914" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H914" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="915" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H915" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
     <row r="916" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H916" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
@@ -13438,541 +13413,353 @@
         <v>315  Helloworld Wheelers Hill</v>
       </c>
     </row>
-    <row r="104" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G104" t="str">
-        <f t="array" aca="1" ref="G104" ca="1">IF(RIGHT(D104,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A104),"]")),_xlfn.TEXTAFTER(CELL("filename",A104),"]"))</f>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>321</v>
+      </c>
+      <c r="B95" t="s">
+        <v>887</v>
+      </c>
+      <c r="C95" t="s">
+        <v>888</v>
+      </c>
+      <c r="D95" t="s">
+        <v>430</v>
+      </c>
+      <c r="E95" t="s">
+        <v>889</v>
+      </c>
+      <c r="F95" t="s">
+        <v>423</v>
+      </c>
+      <c r="G95" t="str">
+        <f t="array" aca="1" ref="G95" ca="1">IF(RIGHT(D95,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A95),"]")),_xlfn.TEXTAFTER(CELL("filename",A95),"]"))</f>
         <v>SOCIAL</v>
       </c>
+      <c r="H95" t="str">
+        <f>_xlfn.CONCAT(A95, " ",C95, " ",D95)</f>
+        <v>321 Richard Dixon</v>
+      </c>
+    </row>
+    <row r="104" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H104" t="str">
         <f t="shared" ref="H104:H129" si="3">_xlfn.CONCAT(A104, " ",C104, " ",D104)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="105" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G105" t="str">
-        <f t="array" aca="1" ref="G105" ca="1">IF(RIGHT(D105,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A105),"]")),_xlfn.TEXTAFTER(CELL("filename",A105),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="105" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H105" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="106" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G106" t="str">
-        <f t="array" aca="1" ref="G106" ca="1">IF(RIGHT(D106,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A106),"]")),_xlfn.TEXTAFTER(CELL("filename",A106),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="106" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H106" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="107" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G107" t="str">
-        <f t="array" aca="1" ref="G107" ca="1">IF(RIGHT(D107,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A107),"]")),_xlfn.TEXTAFTER(CELL("filename",A107),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="107" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H107" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="108" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G108" t="str">
-        <f t="array" aca="1" ref="G108" ca="1">IF(RIGHT(D108,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A108),"]")),_xlfn.TEXTAFTER(CELL("filename",A108),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="108" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H108" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="109" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G109" t="str">
-        <f t="array" aca="1" ref="G109" ca="1">IF(RIGHT(D109,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A109),"]")),_xlfn.TEXTAFTER(CELL("filename",A109),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="109" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H109" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="110" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G110" t="str">
-        <f t="array" aca="1" ref="G110" ca="1">IF(RIGHT(D110,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A110),"]")),_xlfn.TEXTAFTER(CELL("filename",A110),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="110" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H110" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="111" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G111" t="str">
-        <f t="array" aca="1" ref="G111" ca="1">IF(RIGHT(D111,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A111),"]")),_xlfn.TEXTAFTER(CELL("filename",A111),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="111" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H111" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="112" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G112" t="str">
-        <f t="array" aca="1" ref="G112" ca="1">IF(RIGHT(D112,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A112),"]")),_xlfn.TEXTAFTER(CELL("filename",A112),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="112" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H112" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="113" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G113" t="str">
-        <f t="array" aca="1" ref="G113" ca="1">IF(RIGHT(D113,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A113),"]")),_xlfn.TEXTAFTER(CELL("filename",A113),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="113" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H113" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="114" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G114" t="str">
-        <f t="array" aca="1" ref="G114" ca="1">IF(RIGHT(D114,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A114),"]")),_xlfn.TEXTAFTER(CELL("filename",A114),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="114" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H114" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="115" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G115" t="str">
-        <f t="array" aca="1" ref="G115" ca="1">IF(RIGHT(D115,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A115),"]")),_xlfn.TEXTAFTER(CELL("filename",A115),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="115" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H115" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="116" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G116" t="str">
-        <f t="array" aca="1" ref="G116" ca="1">IF(RIGHT(D116,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A116),"]")),_xlfn.TEXTAFTER(CELL("filename",A116),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="116" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H116" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="117" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G117" t="str">
-        <f t="array" aca="1" ref="G117" ca="1">IF(RIGHT(D117,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A117),"]")),_xlfn.TEXTAFTER(CELL("filename",A117),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="117" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H117" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="118" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G118" t="str">
-        <f t="array" aca="1" ref="G118" ca="1">IF(RIGHT(D118,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A118),"]")),_xlfn.TEXTAFTER(CELL("filename",A118),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="118" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H118" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="119" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G119" t="str">
-        <f t="array" aca="1" ref="G119" ca="1">IF(RIGHT(D119,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A119),"]")),_xlfn.TEXTAFTER(CELL("filename",A119),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="119" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H119" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="120" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G120" t="str">
-        <f t="array" aca="1" ref="G120" ca="1">IF(RIGHT(D120,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A120),"]")),_xlfn.TEXTAFTER(CELL("filename",A120),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="120" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H120" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="121" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G121" t="str">
-        <f t="array" aca="1" ref="G121" ca="1">IF(RIGHT(D121,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A121),"]")),_xlfn.TEXTAFTER(CELL("filename",A121),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="121" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H121" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="122" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G122" t="str">
-        <f t="array" aca="1" ref="G122" ca="1">IF(RIGHT(D122,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A122),"]")),_xlfn.TEXTAFTER(CELL("filename",A122),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="122" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H122" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="123" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G123" t="str">
-        <f t="array" aca="1" ref="G123" ca="1">IF(RIGHT(D123,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A123),"]")),_xlfn.TEXTAFTER(CELL("filename",A123),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="123" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H123" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="124" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G124" t="str">
-        <f t="array" aca="1" ref="G124" ca="1">IF(RIGHT(D124,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A124),"]")),_xlfn.TEXTAFTER(CELL("filename",A124),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="124" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H124" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="125" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G125" t="str">
-        <f t="array" aca="1" ref="G125" ca="1">IF(RIGHT(D125,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A125),"]")),_xlfn.TEXTAFTER(CELL("filename",A125),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="125" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H125" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="126" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G126" t="str">
-        <f t="array" aca="1" ref="G126" ca="1">IF(RIGHT(D126,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A126),"]")),_xlfn.TEXTAFTER(CELL("filename",A126),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="126" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H126" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="127" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G127" t="str">
-        <f t="array" aca="1" ref="G127" ca="1">IF(RIGHT(D127,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A127),"]")),_xlfn.TEXTAFTER(CELL("filename",A127),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="127" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H127" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="128" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G128" t="str">
-        <f t="array" aca="1" ref="G128" ca="1">IF(RIGHT(D128,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A128),"]")),_xlfn.TEXTAFTER(CELL("filename",A128),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="128" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H128" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="129" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G129" t="str">
-        <f t="array" aca="1" ref="G129" ca="1">IF(RIGHT(D129,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A129),"]")),_xlfn.TEXTAFTER(CELL("filename",A129),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="129" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H129" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="130" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G130" t="str">
-        <f t="array" aca="1" ref="G130" ca="1">IF(RIGHT(D130,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A130),"]")),_xlfn.TEXTAFTER(CELL("filename",A130),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="130" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H130" t="str">
         <f t="shared" ref="H130:H157" si="4">_xlfn.CONCAT(A130, " ",C130, " ",D130)</f>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="131" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G131" t="str">
-        <f t="array" aca="1" ref="G131" ca="1">IF(RIGHT(D131,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A131),"]")),_xlfn.TEXTAFTER(CELL("filename",A131),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="131" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H131" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="132" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G132" t="str">
-        <f t="array" aca="1" ref="G132" ca="1">IF(RIGHT(D132,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A132),"]")),_xlfn.TEXTAFTER(CELL("filename",A132),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="132" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H132" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="133" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G133" t="str">
-        <f t="array" aca="1" ref="G133" ca="1">IF(RIGHT(D133,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A133),"]")),_xlfn.TEXTAFTER(CELL("filename",A133),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="133" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H133" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="134" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G134" t="str">
-        <f t="array" aca="1" ref="G134" ca="1">IF(RIGHT(D134,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A134),"]")),_xlfn.TEXTAFTER(CELL("filename",A134),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="134" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H134" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="135" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G135" t="str">
-        <f t="array" aca="1" ref="G135" ca="1">IF(RIGHT(D135,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A135),"]")),_xlfn.TEXTAFTER(CELL("filename",A135),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="135" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H135" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="136" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G136" t="str">
-        <f t="array" aca="1" ref="G136" ca="1">IF(RIGHT(D136,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A136),"]")),_xlfn.TEXTAFTER(CELL("filename",A136),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="136" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H136" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="137" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G137" t="str">
-        <f t="array" aca="1" ref="G137" ca="1">IF(RIGHT(D137,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A137),"]")),_xlfn.TEXTAFTER(CELL("filename",A137),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="137" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H137" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="138" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G138" t="str">
-        <f t="array" aca="1" ref="G138" ca="1">IF(RIGHT(D138,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A138),"]")),_xlfn.TEXTAFTER(CELL("filename",A138),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="138" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H138" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="139" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G139" t="str">
-        <f t="array" aca="1" ref="G139" ca="1">IF(RIGHT(D139,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A139),"]")),_xlfn.TEXTAFTER(CELL("filename",A139),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="139" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H139" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="140" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G140" t="str">
-        <f t="array" aca="1" ref="G140" ca="1">IF(RIGHT(D140,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A140),"]")),_xlfn.TEXTAFTER(CELL("filename",A140),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="140" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H140" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="141" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G141" t="str">
-        <f t="array" aca="1" ref="G141" ca="1">IF(RIGHT(D141,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A141),"]")),_xlfn.TEXTAFTER(CELL("filename",A141),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="141" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H141" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="142" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G142" t="str">
-        <f t="array" aca="1" ref="G142" ca="1">IF(RIGHT(D142,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A142),"]")),_xlfn.TEXTAFTER(CELL("filename",A142),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="142" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H142" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="143" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G143" t="str">
-        <f t="array" aca="1" ref="G143" ca="1">IF(RIGHT(D143,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A143),"]")),_xlfn.TEXTAFTER(CELL("filename",A143),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="143" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H143" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="144" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G144" t="str">
-        <f t="array" aca="1" ref="G144" ca="1">IF(RIGHT(D144,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A144),"]")),_xlfn.TEXTAFTER(CELL("filename",A144),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="144" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H144" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="145" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G145" t="str">
-        <f t="array" aca="1" ref="G145" ca="1">IF(RIGHT(D145,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A145),"]")),_xlfn.TEXTAFTER(CELL("filename",A145),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="145" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H145" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="146" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G146" t="str">
-        <f t="array" aca="1" ref="G146" ca="1">IF(RIGHT(D146,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A146),"]")),_xlfn.TEXTAFTER(CELL("filename",A146),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="146" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H146" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="147" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G147" t="str">
-        <f t="array" aca="1" ref="G147" ca="1">IF(RIGHT(D147,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A147),"]")),_xlfn.TEXTAFTER(CELL("filename",A147),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="147" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H147" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="148" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G148" t="str">
-        <f t="array" aca="1" ref="G148" ca="1">IF(RIGHT(D148,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A148),"]")),_xlfn.TEXTAFTER(CELL("filename",A148),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="148" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H148" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="149" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G149" t="str">
-        <f t="array" aca="1" ref="G149" ca="1">IF(RIGHT(D149,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A149),"]")),_xlfn.TEXTAFTER(CELL("filename",A149),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="149" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H149" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="150" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G150" t="str">
-        <f t="array" aca="1" ref="G150" ca="1">IF(RIGHT(D150,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A150),"]")),_xlfn.TEXTAFTER(CELL("filename",A150),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="150" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H150" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="151" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G151" t="str">
-        <f t="array" aca="1" ref="G151" ca="1">IF(RIGHT(D151,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A151),"]")),_xlfn.TEXTAFTER(CELL("filename",A151),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="151" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H151" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="152" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G152" t="str">
-        <f t="array" aca="1" ref="G152" ca="1">IF(RIGHT(D152,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A152),"]")),_xlfn.TEXTAFTER(CELL("filename",A152),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="152" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H152" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="153" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G153" t="str">
-        <f t="array" aca="1" ref="G153" ca="1">IF(RIGHT(D153,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A153),"]")),_xlfn.TEXTAFTER(CELL("filename",A153),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="153" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H153" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="154" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G154" t="str">
-        <f t="array" aca="1" ref="G154" ca="1">IF(RIGHT(D154,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A154),"]")),_xlfn.TEXTAFTER(CELL("filename",A154),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="154" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H154" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="155" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G155" t="str">
-        <f t="array" aca="1" ref="G155" ca="1">IF(RIGHT(D155,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A155),"]")),_xlfn.TEXTAFTER(CELL("filename",A155),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="155" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H155" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="156" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G156" t="str">
-        <f t="array" aca="1" ref="G156" ca="1">IF(RIGHT(D156,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A156),"]")),_xlfn.TEXTAFTER(CELL("filename",A156),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="156" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H156" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
       </c>
     </row>
-    <row r="157" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G157" t="str">
-        <f t="array" aca="1" ref="G157" ca="1">IF(RIGHT(D157,1)="*",_xlfn.CONCAT("LIFE,",_xlfn.TEXTAFTER(CELL("filename",A157),"]")),_xlfn.TEXTAFTER(CELL("filename",A157),"]"))</f>
-        <v>SOCIAL</v>
-      </c>
+    <row r="157" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H157" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  </v>
@@ -13988,6 +13775,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="58a86a11-2690-4781-a7a3-06e5998b1776" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF0DC311990E36488610BB116EE5A325" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="31c82c4d30a69c49951c237e14e34a1c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="58a86a11-2690-4781-a7a3-06e5998b1776" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af2261d2d11220edc89d46b083ccd04f" ns3:_="">
     <xsd:import namespace="58a86a11-2690-4781-a7a3-06e5998b1776"/>
@@ -14163,24 +13967,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{980F6B69-200A-4108-90D7-B3311E4435E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="58a86a11-2690-4781-a7a3-06e5998b1776"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="58a86a11-2690-4781-a7a3-06e5998b1776" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91F166EF-54A0-4472-95C6-CA8654423E63}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9EA0FD7-2406-41FA-97EC-4D4540D99DDC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14196,28 +14007,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91F166EF-54A0-4472-95C6-CA8654423E63}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{980F6B69-200A-4108-90D7-B3311E4435E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="58a86a11-2690-4781-a7a3-06e5998b1776"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>